--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104716_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104716_W29.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3153</v>
+        <v>6.9251</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9956</v>
+        <v>5.8016</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3197</v>
+        <v>1.1235</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4283</v>
+        <v>6.4242</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1796</v>
+        <v>1.1777</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2487</v>
+        <v>5.2465</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6338</v>
+        <v>5.6194</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3217</v>
+        <v>2.313</v>
       </c>
       <c r="L2" t="n">
-        <v>3.312</v>
+        <v>3.3064</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7945</v>
+        <v>0.8048</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1421</v>
+        <v>-1.1353</v>
       </c>
       <c r="O2" t="n">
-        <v>1.9366</v>
+        <v>1.94</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1823</v>
+        <v>-0.2031</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0944</v>
+        <v>-0.2652</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2767</v>
+        <v>0.062</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1739</v>
+        <v>2.6701</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4039</v>
+        <v>0.2218</v>
       </c>
       <c r="F3" t="n">
-        <v>2.77</v>
+        <v>2.4483</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4698</v>
+        <v>2.4694</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3134</v>
+        <v>1.31</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1564</v>
+        <v>1.1594</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1689</v>
+        <v>1.1607</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9453</v>
+        <v>0.9373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2237</v>
+        <v>0.2234</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3008</v>
+        <v>1.3087</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3681</v>
+        <v>0.3727</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9327</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1806</v>
+        <v>3.1868</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9545</v>
+        <v>0.4495</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4834</v>
+        <v>0.3178</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4711</v>
+        <v>0.1317</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.847</v>
+        <v>1.2211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7791</v>
+        <v>0.2968</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0679</v>
+        <v>0.9242</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5884</v>
+        <v>1.5889</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0977</v>
+        <v>1.0971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4907</v>
+        <v>0.4917</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7508</v>
+        <v>1.7464</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6763</v>
+        <v>1.672</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1625</v>
+        <v>-0.1576</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5786</v>
+        <v>-0.5749</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4161</v>
+        <v>0.4173</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3503</v>
+        <v>-0.2799</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1642</v>
+        <v>-0.3115</v>
       </c>
       <c r="U4" t="n">
-        <v>0.186</v>
+        <v>0.0316</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7143</v>
+        <v>1.149</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7964</v>
+        <v>-1.5076</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5107</v>
+        <v>2.6566</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.12</v>
+        <v>-0.1193</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3487</v>
+        <v>1.3496</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4686</v>
+        <v>-1.4689</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5195</v>
+        <v>0.5089</v>
       </c>
       <c r="K5" t="n">
-        <v>2.333</v>
+        <v>2.327</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.8135</v>
+        <v>-1.818</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6395</v>
+        <v>-0.6282</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9843</v>
+        <v>-0.9774</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3449</v>
+        <v>0.3492</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4078</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2104</v>
+        <v>-0.7804</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9527</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2577</v>
+        <v>-0.1297</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1275</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4076</v>
+        <v>-0.0031</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5351</v>
+        <v>0.8625</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5477</v>
+        <v>-1.549</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7844</v>
+        <v>0.784</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3321</v>
+        <v>-2.333</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7129</v>
+        <v>-0.7204</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3862</v>
+        <v>0.3825</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0991</v>
+        <v>-1.1029</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8348</v>
+        <v>-0.8285</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3982</v>
+        <v>0.4016</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2329</v>
+        <v>-1.2301</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.098</v>
+        <v>-0.3624</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8329</v>
+        <v>-0.4114</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2651</v>
+        <v>0.049</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4101</v>
+        <v>1.405</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5013</v>
+        <v>2.4945</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.806</v>
+        <v>-0.2244</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4652</v>
+        <v>-3.0624</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6592</v>
+        <v>2.8379</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3426</v>
+        <v>-0.3464</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1555</v>
+        <v>-0.1551</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1871</v>
+        <v>-0.1912</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2377</v>
+        <v>-1.2525</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5132</v>
+        <v>0.5064</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.7509</v>
+        <v>-1.7589</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8951</v>
+        <v>0.9062</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6688</v>
+        <v>-0.6615</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5638</v>
+        <v>1.5677</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1806</v>
+        <v>3.1868</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4168</v>
+        <v>-0.8373</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0915</v>
+        <v>-0.6717</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3253</v>
+        <v>-0.1656</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8676</v>
+        <v>-0.796</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8385</v>
+        <v>-0.4164</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0291</v>
+        <v>-0.3796</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9438</v>
+        <v>-0.4544</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3351</v>
+        <v>-0.873</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2789</v>
+        <v>0.4186</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2216</v>
+        <v>-0.3257</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1097</v>
+        <v>-0.1691</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1118</v>
+        <v>-0.1566</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1654</v>
+        <v>-0.1287</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2254</v>
+        <v>-0.7039</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3907</v>
+        <v>0.5752</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3631</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0315</v>
+        <v>-0.3902</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8329</v>
+        <v>-0.0907</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8643999999999999</v>
+        <v>-0.2995</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9801</v>
+        <v>-0.8174</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5301</v>
+        <v>-0.4903</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.45</v>
+        <v>-0.3271</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4543</v>
+        <v>-0.9405</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8731</v>
+        <v>0.3359</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4187</v>
+        <v>-1.2763</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3219</v>
+        <v>0.2184</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1668</v>
+        <v>0.1067</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1551</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1324</v>
+        <v>-1.1588</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7063</v>
+        <v>0.2292</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5739</v>
+        <v>-1.3881</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5705</v>
+        <v>0.0743</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2082</v>
+        <v>-0.4811</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3623</v>
+        <v>0.5554</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2123</v>
+        <v>-0.9554</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8321</v>
+        <v>-1.7874</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3802</v>
+        <v>0.832</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.3701</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1623</v>
+        <v>-0.3727</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2449</v>
+        <v>0.0026</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.138</v>
+        <v>-0.8313</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3652</v>
+        <v>-0.0559</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5032</v>
+        <v>-0.7754</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0554</v>
+        <v>0.4613</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2029</v>
+        <v>-0.3168</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2583</v>
+        <v>0.778</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6816</v>
+        <v>2.7316</v>
       </c>
       <c r="S10" t="n">
-        <v>0.416</v>
+        <v>-0.4958</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4419</v>
+        <v>-0.3139</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0259</v>
+        <v>-0.1819</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0913</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0913</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2259</v>
+        <v>-1.0462</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2375</v>
+        <v>-1.1219</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0116</v>
+        <v>0.0757</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0072</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1878</v>
+        <v>-0.1868</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1951</v>
+        <v>0.1952</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0301</v>
+        <v>-0.0289</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1878</v>
+        <v>-0.1868</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.09719999999999999</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1388</v>
+        <v>-0.021</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0416</v>
+        <v>0.1046</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7737</v>
+        <v>-1.5241</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4907</v>
+        <v>-1.2442</v>
       </c>
       <c r="F12" t="n">
-        <v>0.717</v>
+        <v>-0.2799</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3628</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3681</v>
+        <v>1.1605</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0053</v>
+        <v>-1.2455</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8146</v>
+        <v>-0.1431</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.045</v>
+        <v>1.3617</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7696</v>
+        <v>-1.5048</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4518</v>
+        <v>0.0581</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3231</v>
+        <v>-0.2012</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7749</v>
+        <v>0.2593</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7262</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3196</v>
+        <v>0.1057</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0411</v>
+        <v>0.037</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2785</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5456</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6369</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2644</v>
+        <v>-2.7147</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1956</v>
+        <v>-2.7859</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0687</v>
+        <v>0.0712</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6111</v>
+        <v>-2.6137</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1804</v>
+        <v>-2.1798</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4307</v>
+        <v>-0.4339</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.088</v>
+        <v>-1.0969</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.263</v>
+        <v>-2.2655</v>
       </c>
       <c r="L13" t="n">
-        <v>1.175</v>
+        <v>1.1686</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5231</v>
+        <v>-1.5168</v>
       </c>
       <c r="N13" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6058</v>
+        <v>-1.6025</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6297</v>
+        <v>-0.0814</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.3232</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1148</v>
+        <v>0.2418</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.048000000000002</v>
+        <v>4.746499999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.6151</v>
+        <v>-6.099</v>
       </c>
       <c r="F14" t="n">
-        <v>10.6632</v>
+        <v>10.8453</v>
       </c>
       <c r="G14" t="n">
-        <v>4.028799999999999</v>
+        <v>4.012499999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.456299999999998</v>
+        <v>3.4474</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5726000000000011</v>
+        <v>0.5652000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0188</v>
+        <v>4.921100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.175799999999999</v>
+        <v>7.116099999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.156999999999999</v>
+        <v>-2.1948</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9902000000000001</v>
+        <v>-0.9083999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.719600000000001</v>
+        <v>-3.6686</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7296</v>
+        <v>2.7599</v>
       </c>
       <c r="P14" t="n">
-        <v>7.951599999999999</v>
+        <v>7.9672</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.903</v>
+        <v>-15.9343</v>
       </c>
       <c r="R14" t="n">
-        <v>23.8545</v>
+        <v>23.9014</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.4076</v>
+        <v>-2.7174</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.847499999999999</v>
+        <v>-3.1856</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4397999999999999</v>
+        <v>0.468</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.5245</v>
+        <v>-4.5157</v>
       </c>
       <c r="W14" t="n">
-        <v>8.117000000000001</v>
+        <v>8.099600000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.6416</v>
+        <v>-12.6153</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6485</v>
+        <v>6.4667</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1097</v>
+        <v>4.4304</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5387</v>
+        <v>2.0364</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4452</v>
+        <v>-0.4404</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8024</v>
+        <v>0.8064</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2476</v>
+        <v>-1.2468</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4995</v>
+        <v>0.4889</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3503</v>
+        <v>2.3442</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.8508</v>
+        <v>-1.8553</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9447</v>
+        <v>-0.9293</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5479</v>
+        <v>-1.5378</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6032</v>
+        <v>0.6085</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9534</v>
+        <v>-2.9592</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0499</v>
+        <v>0.8781</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3026</v>
+        <v>0.0483</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3525</v>
+        <v>0.8299</v>
       </c>
       <c r="V15" t="n">
-        <v>6.7253</v>
+        <v>6.7119</v>
       </c>
       <c r="W15" t="n">
-        <v>6.8663</v>
+        <v>6.8524</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.141</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3817</v>
+        <v>1.2469</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3299</v>
+        <v>-0.6894</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9482</v>
+        <v>1.9364</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5669</v>
+        <v>-1.7577</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7033</v>
+        <v>-2.3894</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1364</v>
+        <v>0.6317</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7997</v>
+        <v>-1.3732</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4335</v>
+        <v>-0.8661</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6338</v>
+        <v>-0.5071</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7672</v>
+        <v>-0.3846</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2698</v>
+        <v>-1.5233</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5026</v>
+        <v>1.1388</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8175</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9534</v>
+        <v>-0.6829</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8159</v>
+        <v>0.1451</v>
       </c>
       <c r="T16" t="n">
-        <v>3.9005</v>
+        <v>-0.2676</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0847</v>
+        <v>0.4127</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9502</v>
+        <v>1.4937</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1825</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2323</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6388</v>
+        <v>0.7084</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3083</v>
+        <v>-0.3107</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.0192</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0762</v>
+        <v>1.0802</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4651</v>
+        <v>0.4677</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6112</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0891</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9871</v>
+        <v>0.9912</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4132</v>
+        <v>0.416</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5739</v>
+        <v>0.5752</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4821</v>
+        <v>-0.4204</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3975</v>
+        <v>-0.3997</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0847</v>
+        <v>-0.0207</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0405</v>
+        <v>-0.1451</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4961</v>
+        <v>-0.9967</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5366</v>
+        <v>0.8517</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7589</v>
+        <v>-0.8454</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.39</v>
+        <v>0.3359</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6311</v>
+        <v>-1.1813</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3598</v>
+        <v>-0.7179</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8572</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5026</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3991</v>
+        <v>-0.1275</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5328</v>
+        <v>0.3014</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1338</v>
+        <v>-0.4289</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.6816</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0447</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0596</v>
+        <v>0.0174</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0915</v>
+        <v>-0.2788</v>
       </c>
       <c r="U18" t="n">
-        <v>0.032</v>
+        <v>0.2962</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6369</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1164</v>
+        <v>-0.1641</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9947</v>
+        <v>0.3578</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8782</v>
+        <v>-0.5219</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8466</v>
+        <v>0.7988</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3351</v>
+        <v>0.4766</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1817</v>
+        <v>0.3222</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7171</v>
+        <v>1.4707</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>1.3962</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7516</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1295</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3005</v>
+        <v>-0.9196</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4301</v>
+        <v>0.2477</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6816</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0486</v>
+        <v>0.5819</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2776</v>
+        <v>0.253</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3262</v>
+        <v>0.3289</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3037</v>
+        <v>-0.3057</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4837</v>
+        <v>-0.86</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7874</v>
+        <v>0.5543</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7945</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4756</v>
+        <v>-0.3047</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3189</v>
+        <v>-0.3159</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4743</v>
+        <v>-0.7207</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3998</v>
+        <v>0.0689</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-0.7896</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6798999999999999</v>
+        <v>0.1002</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9242</v>
+        <v>-0.3736</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2443</v>
+        <v>0.4738</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4544</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3631</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4474</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3725</v>
+        <v>-0.0907</v>
       </c>
       <c r="U20" t="n">
-        <v>0.075</v>
+        <v>-0.0011</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
+        <v>1.0895</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.0913</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.516</v>
+        <v>-0.3085</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9727</v>
+        <v>-0.7772</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4567</v>
+        <v>0.4687</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6221</v>
+        <v>2.3676</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3066</v>
+        <v>2.9904</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3156</v>
+        <v>-0.6227</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7198</v>
+        <v>3.8841</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06909999999999999</v>
+        <v>3.7954</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7889</v>
+        <v>0.0887</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0977</v>
+        <v>-1.5164</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3757</v>
+        <v>-0.805</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4733</v>
+        <v>-0.7114</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6816</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-3.8697</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4544</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3035</v>
+        <v>0.7619</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2082</v>
+        <v>-0.4046</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0953</v>
+        <v>1.1664</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0913</v>
+        <v>-1.6169</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0913</v>
+        <v>-0.387</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7617</v>
+        <v>-0.8064</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4571</v>
+        <v>-0.4082</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6954</v>
+        <v>-0.3982</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3739</v>
+        <v>-1.5624</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9964</v>
+        <v>-2.7025</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6225000000000001</v>
+        <v>1.1401</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9018</v>
+        <v>-0.8051</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8079</v>
+        <v>-1.4381</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0939</v>
+        <v>0.633</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5278</v>
+        <v>-0.7573</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8115</v>
+        <v>-1.2643</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7163</v>
+        <v>0.5071</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8622</v>
+        <v>-2.9592</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0447</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3003</v>
+        <v>1.628</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1105</v>
+        <v>1.1772</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4108</v>
+        <v>0.4509</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6185</v>
+        <v>0.949</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3862</v>
+        <v>2.1789</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2323</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7419</v>
+        <v>-1.8523</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2814</v>
+        <v>-2.5995</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5394</v>
+        <v>0.7472</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1907</v>
+        <v>0.186</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1195</v>
+        <v>-1.1199</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3102</v>
+        <v>1.3059</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3063</v>
+        <v>1.2892</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3983</v>
+        <v>0.389</v>
       </c>
       <c r="L23" t="n">
-        <v>0.908</v>
+        <v>0.9002</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1157</v>
+        <v>-1.1032</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5178</v>
+        <v>-1.5089</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4021</v>
+        <v>0.4057</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1151</v>
+        <v>-0.2173</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9527</v>
+        <v>-0.2466</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1624</v>
+        <v>0.0294</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5906</v>
+        <v>-3.0105</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2331</v>
+        <v>-3.8945</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6425</v>
+        <v>0.8839</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1203</v>
+        <v>-1.1177</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6244</v>
+        <v>-0.6233</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.496</v>
+        <v>-0.4944</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9721</v>
+        <v>-0.979</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6619</v>
+        <v>-0.6657</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3102</v>
+        <v>-0.3132</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1482</v>
+        <v>-0.1387</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0375</v>
+        <v>0.0424</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1857</v>
+        <v>-0.1811</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0574</v>
+        <v>0.6331</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3417</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.9747</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3917</v>
+        <v>-1.3877</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.5511</v>
+        <v>-1.5455</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7272</v>
+        <v>-5.0893</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.843</v>
+        <v>-5.0972</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1158</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.104</v>
+        <v>-2.101</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.387</v>
+        <v>-1.3845</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.717</v>
+        <v>-0.7165</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7125</v>
+        <v>-1.7174</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4396</v>
+        <v>-1.4414</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.273</v>
+        <v>-0.276</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3915</v>
+        <v>-0.3836</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0526</v>
+        <v>0.0568</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.444</v>
+        <v>-0.4405</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.2881</v>
       </c>
       <c r="T25" t="n">
-        <v>0.322</v>
+        <v>0.0834</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3267</v>
+        <v>0.2047</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.048</v>
+        <v>-3.259899999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.6631</v>
+        <v>-10.8452</v>
       </c>
       <c r="F26" t="n">
-        <v>6.614799999999999</v>
+        <v>7.5856</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.028700000000001</v>
+        <v>-4.0125</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.4562</v>
+        <v>-3.4473</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5725999999999999</v>
+        <v>-0.5652999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9900000000000007</v>
+        <v>0.9084999999999996</v>
       </c>
       <c r="K26" t="n">
-        <v>3.719599999999999</v>
+        <v>3.668600000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.729500000000001</v>
+        <v>-2.76</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.0188</v>
+        <v>-4.9211</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.175900000000001</v>
+        <v>-7.1159</v>
       </c>
       <c r="O26" t="n">
-        <v>2.157099999999999</v>
+        <v>2.1949</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.951600000000001</v>
+        <v>-7.9673</v>
       </c>
       <c r="Q26" t="n">
-        <v>-23.8545</v>
+        <v>-23.9013</v>
       </c>
       <c r="R26" t="n">
-        <v>15.9031</v>
+        <v>15.9344</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4079</v>
+        <v>4.2041</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4396999999999998</v>
+        <v>-0.4678</v>
       </c>
       <c r="U26" t="n">
-        <v>3.8476</v>
+        <v>4.672000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>4.524299999999999</v>
+        <v>4.5158</v>
       </c>
       <c r="W26" t="n">
-        <v>12.6415</v>
+        <v>12.6153</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.1172</v>
+        <v>-8.0997</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104716_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104716_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-12.6153</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.23</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.23</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.5455</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104716_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.0997</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
